--- a/public/contoh_excel/TEMPLATE INPUT TAGIHAN.xlsx
+++ b/public/contoh_excel/TEMPLATE INPUT TAGIHAN.xlsx
@@ -15,27 +15,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
-  <si>
-    <t>NOCUST</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
+  <si>
+    <t>NIS</t>
   </si>
   <si>
     <t>NOMINAL</t>
   </si>
   <si>
-    <t>NMTagihan</t>
-  </si>
-  <si>
-    <t>BILLPERIOD</t>
-  </si>
-  <si>
-    <t>BTA</t>
-  </si>
-  <si>
-    <t>isNYICIL</t>
-  </si>
-  <si>
-    <t>BULAN AGUSTUS</t>
+    <t>NAMA_TAGIHAN</t>
+  </si>
+  <si>
+    <t>PERIODE</t>
+  </si>
+  <si>
+    <t>TAHUN_AKADEMIK</t>
+  </si>
+  <si>
+    <t>CICIL</t>
+  </si>
+  <si>
+    <t>1234567801</t>
+  </si>
+  <si>
+    <t>BULAN SEPTEMBER</t>
+  </si>
+  <si>
+    <t>202609</t>
+  </si>
+  <si>
+    <t>2026/2027</t>
   </si>
 </sst>
 </file>
@@ -390,10 +399,10 @@
   <cols>
     <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="6.998" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -417,20 +426,20 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2">
-        <v>1301154344</v>
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>202608</v>
-      </c>
-      <c r="E2">
-        <v>202608</v>
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
       <c r="F2">
         <v>1</v>
